--- a/ISOC_result/Living_room_11/Living_room_result_of_performance_index.xlsx
+++ b/ISOC_result/Living_room_11/Living_room_result_of_performance_index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\ISOC\ISOC_result\Living_room_11\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF60C193-0001-4A4F-A94D-00345B69492D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EB14FD6-D7B4-43E2-9272-8FEFA8B412EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1310,11 +1310,11 @@
   <dimension ref="A1:E45"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -2083,7 +2083,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E45" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
